--- a/03_Outputs/all/01_TablasDescriptivas/idx13_saludmental_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx13_saludmental_vr.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.945615416244032</v>
+        <v>4.94561541624403</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>3.58888242279621</v>
+        <v>3.588882422796204</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.27882424096073</v>
+        <v>1.278824240960731</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9905433984387301</v>
+        <v>0.9905433984387303</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.5064572730113543</v>
+        <v>0.5064572730113548</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.3478121056220403</v>
+        <v>0.3478121056220399</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.1808369160628964</v>
+        <v>0.1808369160628958</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.07913941695469592</v>
+        <v>0.0791394169546962</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.05340160401048527</v>
+        <v>0.05340160401048531</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.01499318459693417</v>
+        <v>0.01499318459693419</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.01293371265819927</v>
+        <v>0.01293371265819926</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.0005603086436913461</v>
+        <v>0.0005603086436913514</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>4.945615416244032</v>
+        <v>4.94561541624403</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>8.534497839040242</v>
+        <v>8.534497839040235</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>9.813322080000972</v>
+        <v>9.813322080000965</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>11.31032275145106</v>
+        <v>11.31032275145105</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>11.6581348570731</v>
+        <v>11.65813485707309</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>11.91811119009069</v>
+        <v>11.91811119009068</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>11.98650597869811</v>
+        <v>11.9865059786981</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>11.99943969135631</v>
+        <v>11.9994396913563</v>
       </c>
       <c r="C24">
         <v>11</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>11.99999999999999</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>41.2134618020336</v>
+        <v>41.21346180203361</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>29.90735352330175</v>
+        <v>29.90735352330172</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>10.65686867467275</v>
+        <v>10.65686867467277</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>8.25452832032275</v>
+        <v>8.254528320322757</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>4.22047727509462</v>
+        <v>4.220477275094626</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>2.898434213517002</v>
+        <v>2.898434213517001</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>1.506974300524137</v>
+        <v>1.506974300524133</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.6594951412891327</v>
+        <v>0.6594951412891353</v>
       </c>
       <c r="C33">
         <v>8</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.4450133667540439</v>
+        <v>0.4450133667540445</v>
       </c>
       <c r="C34">
         <v>9</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.1249432049744514</v>
+        <v>0.1249432049744516</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.004669238697427885</v>
+        <v>0.004669238697427931</v>
       </c>
       <c r="C37">
         <v>12</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>41.2134618020336</v>
+        <v>41.21346180203361</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>71.12081532533536</v>
+        <v>71.12081532533533</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>90.03221232033086</v>
+        <v>90.03221232033084</v>
       </c>
       <c r="C41">
         <v>4</v>
